--- a/DE samenwerken/week 5/DWH_logboek1.xlsx
+++ b/DE samenwerken/week 5/DWH_logboek1.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -469,19 +469,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -499,19 +495,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -529,19 +521,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -559,19 +547,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -589,19 +573,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -619,19 +599,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +625,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -679,19 +651,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -709,19 +677,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -739,19 +703,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -769,19 +729,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -799,19 +755,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -829,19 +781,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -859,19 +807,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -889,19 +833,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -919,19 +859,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -949,19 +885,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -979,19 +911,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1009,19 +937,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1039,19 +963,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1069,19 +989,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1099,19 +1015,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,19 +1041,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1159,19 +1067,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1189,19 +1093,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Already current</t>
-        </is>
-      </c>
+          <t>NO CHANGE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1214,20 +1114,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1240,20 +1144,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1266,20 +1174,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1292,20 +1204,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1318,20 +1234,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1344,20 +1264,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1370,20 +1294,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1396,20 +1324,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1422,20 +1354,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1448,20 +1384,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1474,20 +1414,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1500,20 +1444,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1526,20 +1474,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1552,20 +1504,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1578,20 +1534,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1609,7 +1569,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1617,7 +1577,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1635,7 +1595,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1643,7 +1603,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1661,7 +1621,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1669,7 +1629,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1687,7 +1647,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1695,7 +1655,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1713,7 +1673,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -1721,7 +1681,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1739,7 +1699,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1747,7 +1707,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1765,7 +1725,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1773,7 +1733,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1791,7 +1751,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1799,7 +1759,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1817,7 +1777,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1825,7 +1785,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1843,7 +1803,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1851,7 +1811,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1869,7 +1829,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1877,7 +1837,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1895,7 +1855,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1903,7 +1863,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1921,7 +1881,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1929,7 +1889,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1947,7 +1907,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1955,7 +1915,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1973,7 +1933,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1981,7 +1941,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1999,7 +1959,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -2007,7 +1967,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2025,7 +1985,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -2033,7 +1993,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2051,7 +2011,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -2059,7 +2019,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2077,7 +2037,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -2085,7 +2045,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2103,7 +2063,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -2111,7 +2071,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2129,7 +2089,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -2137,7 +2097,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2155,7 +2115,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -2163,7 +2123,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2181,7 +2141,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2189,7 +2149,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2207,7 +2167,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -2215,7 +2175,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2233,7 +2193,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2241,7 +2201,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2259,7 +2219,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2267,7 +2227,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2285,7 +2245,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2293,7 +2253,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2311,7 +2271,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2319,7 +2279,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2337,7 +2297,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2345,7 +2305,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2363,7 +2323,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -2371,7 +2331,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2389,7 +2349,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2397,7 +2357,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2415,7 +2375,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -2423,7 +2383,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2441,7 +2401,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -2449,7 +2409,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2467,7 +2427,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -2475,7 +2435,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2493,7 +2453,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -2501,7 +2461,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2519,7 +2479,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -2527,7 +2487,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2545,7 +2505,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -2553,7 +2513,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2571,7 +2531,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -2579,7 +2539,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2597,7 +2557,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -2605,7 +2565,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2623,7 +2583,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -2631,7 +2591,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2649,7 +2609,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -2657,7 +2617,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2675,7 +2635,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -2683,7 +2643,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,7 +2661,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -2709,7 +2669,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2727,7 +2687,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -2735,7 +2695,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2753,7 +2713,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -2761,7 +2721,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2779,7 +2739,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -2787,7 +2747,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2805,7 +2765,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
@@ -2813,7 +2773,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,7 +2791,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -2839,7 +2799,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2857,7 +2817,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -2865,7 +2825,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2883,7 +2843,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
@@ -2891,7 +2851,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2909,7 +2869,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -2917,7 +2877,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2935,7 +2895,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -2943,7 +2903,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2961,7 +2921,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -2969,7 +2929,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2987,7 +2947,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -2995,7 +2955,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3013,7 +2973,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -3021,7 +2981,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3039,7 +2999,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3047,7 +3007,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3065,7 +3025,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -3073,7 +3033,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3091,7 +3051,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -3099,7 +3059,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3117,7 +3077,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -3125,7 +3085,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3143,7 +3103,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
@@ -3151,7 +3111,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3169,7 +3129,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -3177,7 +3137,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3195,7 +3155,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -3203,7 +3163,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3221,7 +3181,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -3229,7 +3189,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3247,7 +3207,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
@@ -3255,7 +3215,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3273,7 +3233,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
@@ -3281,7 +3241,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3299,7 +3259,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
@@ -3307,7 +3267,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3325,7 +3285,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
@@ -3333,7 +3293,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3351,7 +3311,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
@@ -3359,7 +3319,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3377,7 +3337,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -3385,7 +3345,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3403,7 +3363,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -3411,7 +3371,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3429,7 +3389,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -3437,7 +3397,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3455,7 +3415,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -3463,7 +3423,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3481,7 +3441,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -3489,7 +3449,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3507,7 +3467,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
@@ -3515,7 +3475,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3533,7 +3493,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>NO CHANGE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -3541,7 +3501,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3554,20 +3514,24 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3580,20 +3544,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3606,20 +3574,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3632,20 +3604,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3658,20 +3634,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3684,20 +3664,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3710,20 +3694,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3736,20 +3724,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3762,20 +3754,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3788,20 +3784,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3814,20 +3814,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3840,20 +3844,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3866,20 +3874,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ON CONFLICT clause does not match any PRIMARY KEY or UNIQUE constraint</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3905,7 +3917,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3931,7 +3943,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3957,7 +3969,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3983,7 +3995,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4009,7 +4021,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4035,7 +4047,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4061,7 +4073,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4087,7 +4099,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4113,7 +4125,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4139,7 +4151,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4165,7 +4177,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4191,7 +4203,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4217,7 +4229,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4243,7 +4255,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4269,7 +4281,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4295,7 +4307,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4321,7 +4333,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4347,7 +4359,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4373,7 +4385,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4399,7 +4411,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4425,7 +4437,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4451,7 +4463,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4477,7 +4489,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4503,7 +4515,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4529,7 +4541,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4555,7 +4567,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4581,7 +4593,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4607,7 +4619,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4633,7 +4645,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4659,7 +4671,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4685,7 +4697,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4711,7 +4723,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4737,7 +4749,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4763,7 +4775,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4789,7 +4801,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4815,7 +4827,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4841,7 +4853,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4867,7 +4879,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4893,7 +4905,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4919,7 +4931,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4945,7 +4957,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4971,7 +4983,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4997,7 +5009,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5023,7 +5035,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5049,7 +5061,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5075,7 +5087,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5101,7 +5113,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5127,7 +5139,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5153,7 +5165,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5179,7 +5191,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5205,7 +5217,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5231,7 +5243,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5257,7 +5269,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5283,7 +5295,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5309,7 +5321,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5335,7 +5347,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5361,7 +5373,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5387,7 +5399,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5413,7 +5425,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5439,7 +5451,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5465,7 +5477,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5491,7 +5503,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5517,7 +5529,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5543,7 +5555,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5569,7 +5581,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5595,7 +5607,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5621,7 +5633,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5647,7 +5659,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5673,7 +5685,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5699,7 +5711,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5725,7 +5737,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5751,7 +5763,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5777,7 +5789,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5803,7 +5815,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5829,7 +5841,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5855,7 +5867,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5881,7 +5893,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5907,7 +5919,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5933,7 +5945,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5959,7 +5971,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5985,7 +5997,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6011,7 +6023,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6037,7 +6049,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6063,7 +6075,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6089,7 +6101,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6115,7 +6127,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6141,7 +6153,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6167,7 +6179,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6193,7 +6205,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6219,7 +6231,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6245,7 +6257,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6271,7 +6283,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6297,7 +6309,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6323,7 +6335,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6349,7 +6361,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6375,7 +6387,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6401,7 +6413,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6427,7 +6439,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6453,7 +6465,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6479,7 +6491,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6505,7 +6517,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6531,7 +6543,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6557,7 +6569,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6583,7 +6595,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6609,7 +6621,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6635,7 +6647,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6661,7 +6673,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6687,7 +6699,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6713,7 +6725,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6739,7 +6751,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6765,7 +6777,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6791,7 +6803,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:14</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6817,7 +6829,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6843,7 +6855,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6869,7 +6881,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6895,7 +6907,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6921,7 +6933,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6947,7 +6959,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6973,7 +6985,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6999,7 +7011,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7025,7 +7037,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7051,7 +7063,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7077,7 +7089,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7103,7 +7115,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7129,7 +7141,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7155,7 +7167,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7181,7 +7193,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7207,7 +7219,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7233,7 +7245,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7259,7 +7271,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7285,7 +7297,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7311,7 +7323,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7337,7 +7349,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7363,7 +7375,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7389,7 +7401,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7415,7 +7427,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7441,7 +7453,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7467,7 +7479,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7493,7 +7505,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7519,7 +7531,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7545,7 +7557,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:13</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7571,7 +7583,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7597,7 +7609,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7623,7 +7635,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7649,7 +7661,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7675,7 +7687,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7701,7 +7713,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7727,7 +7739,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7753,7 +7765,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-04-15 16:13:14</t>
+          <t>2026-04-16 13:55:15</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
